--- a/Young_etal_2013/Young_etal_2013.xlsx
+++ b/Young_etal_2013/Young_etal_2013.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10409"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo M1 Trait Data/Young_etal_2013/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/Young_etal_2013/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="227" documentId="8_{87A38D43-FB4B-164F-A4C4-1EF284968B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4856BAC6-2AC0-D64F-B9B2-A119751521AA}"/>
+  <xr:revisionPtr revIDLastSave="228" documentId="8_{87A38D43-FB4B-164F-A4C4-1EF284968B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0ED6C3B-6742-9A40-A29D-6BF541F2ACAD}"/>
   <bookViews>
-    <workbookView xWindow="17180" yWindow="3120" windowWidth="29160" windowHeight="16420" xr2:uid="{F73B9AFC-2043-5248-B344-8270F8690E1E}"/>
+    <workbookView xWindow="37840" yWindow="1420" windowWidth="29160" windowHeight="16420" activeTab="1" xr2:uid="{F73B9AFC-2043-5248-B344-8270F8690E1E}"/>
   </bookViews>
   <sheets>
     <sheet name="published Table 1" sheetId="1" r:id="rId1"/>
@@ -839,9 +839,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -879,7 +879,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -985,7 +985,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1127,7 +1127,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1138,6 +1138,7 @@
   <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="31" customWidth="1"/>
     <col min="2" max="11" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2100,17 +2101,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1692e213da595cbe2f8b4fd37e6b2a91">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="27148b6917a39128a8d85a83794e1a7d" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -2132,6 +2135,8 @@
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2197,6 +2202,16 @@
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
@@ -2340,56 +2355,39 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57F5FEC8-D08D-4145-ABC7-B3A613D5D4C0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A919DF6-03A6-4DB7-B849-1860463CC392}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C8F1AC2-6B39-4F5D-BF4A-736165E42A2F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7E6BFA4-669B-45B7-BC6F-A16FDED6402E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57F5FEC8-D08D-4145-ABC7-B3A613D5D4C0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Young_etal_2013/Young_etal_2013.xlsx
+++ b/Young_etal_2013/Young_etal_2013.xlsx
@@ -2112,8 +2112,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -2137,6 +2137,8 @@
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2211,6 +2213,16 @@
     <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -2381,7 +2393,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A919DF6-03A6-4DB7-B849-1860463CC392}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C94AF1C8-3037-418F-B5C8-CD8E5EFDADE0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Young_etal_2013/Young_etal_2013.xlsx
+++ b/Young_etal_2013/Young_etal_2013.xlsx
@@ -2112,8 +2112,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -2137,6 +2137,8 @@
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2211,6 +2213,16 @@
     <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -2381,7 +2393,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A919DF6-03A6-4DB7-B849-1860463CC392}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9574DCAA-0DC8-4FD9-B486-4FC4712ACA66}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Young_etal_2013/Young_etal_2013.xlsx
+++ b/Young_etal_2013/Young_etal_2013.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/Young_etal_2013/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="228" documentId="8_{87A38D43-FB4B-164F-A4C4-1EF284968B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0ED6C3B-6742-9A40-A29D-6BF541F2ACAD}"/>
+  <xr:revisionPtr revIDLastSave="237" documentId="8_{87A38D43-FB4B-164F-A4C4-1EF284968B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8980D19-2394-E748-B191-5B443867FCE5}"/>
   <bookViews>
-    <workbookView xWindow="37840" yWindow="1420" windowWidth="29160" windowHeight="16420" activeTab="1" xr2:uid="{F73B9AFC-2043-5248-B344-8270F8690E1E}"/>
+    <workbookView xWindow="52660" yWindow="280" windowWidth="29160" windowHeight="16420" activeTab="1" xr2:uid="{F73B9AFC-2043-5248-B344-8270F8690E1E}"/>
   </bookViews>
   <sheets>
     <sheet name="published Table 1" sheetId="1" r:id="rId1"/>
@@ -2101,14 +2101,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2367,39 +2365,56 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57F5FEC8-D08D-4145-ABC7-B3A613D5D4C0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C8F1AC2-6B39-4F5D-BF4A-736165E42A2F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9574DCAA-0DC8-4FD9-B486-4FC4712ACA66}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9574DCAA-0DC8-4FD9-B486-4FC4712ACA66}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C8F1AC2-6B39-4F5D-BF4A-736165E42A2F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57F5FEC8-D08D-4145-ABC7-B3A613D5D4C0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Young_etal_2013/Young_etal_2013.xlsx
+++ b/Young_etal_2013/Young_etal_2013.xlsx
@@ -2112,8 +2112,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -2137,6 +2137,8 @@
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2211,6 +2213,16 @@
     <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -2381,7 +2393,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A919DF6-03A6-4DB7-B849-1860463CC392}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D73A76B1-ADC8-4590-81A7-17B74D4A9F5C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
